--- a/branches/feature-s3-annotation-ig/ValueSet-vs-senologie-r-status.xlsx
+++ b/branches/feature-s3-annotation-ig/ValueSet-vs-senologie-r-status.xlsx
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Resektionsstatus R0/R1/R2/RX als SNOMED-Codes.</t>
+    <t>Resektionsstatus R0/R1/R2/RX nach UICC, kodiert mit SNOMED CT (SCT#135252x00x).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -103,25 +103,25 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>r-0</t>
+    <t>1352526005</t>
   </si>
   <si>
     <t>R0 — kein Residualtumor</t>
   </si>
   <si>
-    <t>r-1</t>
+    <t>1352529003</t>
   </si>
   <si>
     <t>R1 — mikroskopischer Residualtumor</t>
   </si>
   <si>
-    <t>r-2</t>
+    <t>1352528006</t>
   </si>
   <si>
     <t>R2 — makroskopischer Residualtumor</t>
   </si>
   <si>
-    <t>r-x</t>
+    <t>1352527001</t>
   </si>
   <si>
     <t>RX — nicht beurteilbar</t>
@@ -130,7 +130,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://www.senologie.org/fhir/CodeSystem/form-helper</t>
+    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>Level</t>
